--- a/data/trans_orig/P2C_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R2-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2007</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>191187</t>
+          <t>192187</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>239538</t>
+          <t>240614</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>237023</t>
+          <t>237303</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>287657</t>
+          <t>286885</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>441287</t>
+          <t>441490</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>512707</t>
+          <t>511954</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,03%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>454474</t>
+          <t>453398</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>502825</t>
+          <t>501825</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>400694</t>
+          <t>401466</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>451328</t>
+          <t>451048</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>869656</t>
+          <t>870409</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>941076</t>
+          <t>940873</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,06%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>266396</t>
+          <t>268618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>328633</t>
+          <t>324301</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>307787</t>
+          <t>307578</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>370139</t>
+          <t>367824</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>592004</t>
+          <t>589580</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>673383</t>
+          <t>673921</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,91%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>633167</t>
+          <t>637499</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>695404</t>
+          <t>693182</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>598254</t>
+          <t>600569</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>660606</t>
+          <t>660815</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1256810</t>
+          <t>1256272</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1338189</t>
+          <t>1340613</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,45%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>170030</t>
+          <t>167854</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>219308</t>
+          <t>219121</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>205016</t>
+          <t>203375</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>252728</t>
+          <t>252239</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>389522</t>
+          <t>390753</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>459543</t>
+          <t>460137</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,78%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>459201</t>
+          <t>459388</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>508479</t>
+          <t>510655</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>431113</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>478825</t>
+          <t>480466</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>902807</t>
+          <t>902213</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>972828</t>
+          <t>971597</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,32%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>227032</t>
+          <t>227202</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>278633</t>
+          <t>280920</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>307198</t>
+          <t>310265</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>369182</t>
+          <t>369336</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>548297</t>
+          <t>547132</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>632577</t>
+          <t>631088</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>663589</t>
+          <t>661302</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>715190</t>
+          <t>715020</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>669430</t>
+          <t>669276</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>731414</t>
+          <t>728347</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1348257</t>
+          <t>1349746</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1432537</t>
+          <t>1433702</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,38%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>899229</t>
+          <t>902370</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1010203</t>
+          <t>1007998</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1110807</t>
+          <t>1112673</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1218215</t>
+          <t>1224850</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2042280</t>
+          <t>2052399</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2190236</t>
+          <t>2205057</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2266340</t>
+          <t>2268545</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2377314</t>
+          <t>2374173</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2160982</t>
+          <t>2154347</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2268390</t>
+          <t>2266524</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4465505</t>
+          <t>4450684</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4613461</t>
+          <t>4603342</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,16%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2012</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>304724</t>
+          <t>302075</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>355353</t>
+          <t>356761</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>334126</t>
+          <t>332117</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>389167</t>
+          <t>388641</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>657916</t>
+          <t>657482</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>735263</t>
+          <t>730272</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,14%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>348116</t>
+          <t>346708</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>398745</t>
+          <t>401394</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>307883</t>
+          <t>308409</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>362924</t>
+          <t>364933</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>665256</t>
+          <t>670247</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>742603</t>
+          <t>743037</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,05%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>459723</t>
+          <t>460161</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>526082</t>
+          <t>523635</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>543506</t>
+          <t>540486</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>605210</t>
+          <t>604273</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1020606</t>
+          <t>1019623</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1110662</t>
+          <t>1110375</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,16%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>491865</t>
+          <t>494312</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>558224</t>
+          <t>557786</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>426974</t>
+          <t>427911</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>488678</t>
+          <t>491698</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>939469</t>
+          <t>939756</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1029525</t>
+          <t>1030508</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,27%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>309000</t>
+          <t>307038</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>369067</t>
+          <t>365298</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>382586</t>
+          <t>384843</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>441786</t>
+          <t>443842</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>707422</t>
+          <t>707368</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>790395</t>
+          <t>793900</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,73%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>388556</t>
+          <t>392325</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>448623</t>
+          <t>450585</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>335388</t>
+          <t>333332</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>394588</t>
+          <t>392331</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>744402</t>
+          <t>740897</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>827375</t>
+          <t>827429</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>343068</t>
+          <t>344320</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>402836</t>
+          <t>404429</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>457412</t>
+          <t>455821</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>523310</t>
+          <t>519125</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>817465</t>
+          <t>813937</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>906268</t>
+          <t>910770</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,55%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>544903</t>
+          <t>543310</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>604671</t>
+          <t>603419</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>528591</t>
+          <t>532776</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>594489</t>
+          <t>596080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1093372</t>
+          <t>1088870</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1182175</t>
+          <t>1185703</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,3%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1478659</t>
+          <t>1475400</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1593946</t>
+          <t>1592229</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1776561</t>
+          <t>1777181</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1901319</t>
+          <t>1901415</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3270192</t>
+          <t>3291292</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3452205</t>
+          <t>3461983</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,56%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1832833</t>
+          <t>1834550</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1948120</t>
+          <t>1951379</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1656990</t>
+          <t>1656894</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1781748</t>
+          <t>1781128</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3532883</t>
+          <t>3523105</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3714896</t>
+          <t>3693796</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,88%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2016</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>204368</t>
+          <t>204026</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>254109</t>
+          <t>255131</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>222286</t>
+          <t>225147</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>273020</t>
+          <t>273264</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>442775</t>
+          <t>440353</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>516508</t>
+          <t>510169</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>37,86%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>420691</t>
+          <t>419669</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>470432</t>
+          <t>470774</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>399819</t>
+          <t>399575</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>450553</t>
+          <t>447692</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>831131</t>
+          <t>837470</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>904864</t>
+          <t>907286</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,32%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>319556</t>
+          <t>316785</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>378636</t>
+          <t>379648</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>418193</t>
+          <t>419003</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>482772</t>
+          <t>483163</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>752799</t>
+          <t>750028</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>843225</t>
+          <t>842687</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,8%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>643795</t>
+          <t>642783</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>702875</t>
+          <t>705646</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>560141</t>
+          <t>559750</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>624720</t>
+          <t>623910</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1222119</t>
+          <t>1222657</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1312545</t>
+          <t>1315316</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,69%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>210654</t>
+          <t>210004</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>264744</t>
+          <t>262767</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>286348</t>
+          <t>287229</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>341743</t>
+          <t>340617</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>512736</t>
+          <t>512830</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>587789</t>
+          <t>589078</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,14%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>494808</t>
+          <t>496785</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>548898</t>
+          <t>549548</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>443268</t>
+          <t>444394</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>498663</t>
+          <t>497782</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>956774</t>
+          <t>955485</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1031827</t>
+          <t>1031733</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>226076</t>
+          <t>225033</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>282261</t>
+          <t>280594</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>324913</t>
+          <t>327801</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>390288</t>
+          <t>392616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>568087</t>
+          <t>568053</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>650513</t>
+          <t>652741</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,94%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>655306</t>
+          <t>656973</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>711491</t>
+          <t>712534</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>653491</t>
+          <t>651163</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>718866</t>
+          <t>715978</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1330833</t>
+          <t>1328605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1413259</t>
+          <t>1413293</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1007995</t>
+          <t>1008815</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1110714</t>
+          <t>1117687</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1312864</t>
+          <t>1316269</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1434726</t>
+          <t>1436404</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2353086</t>
+          <t>2353450</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2516177</t>
+          <t>2514349</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,24%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2283636</t>
+          <t>2276663</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2386355</t>
+          <t>2385535</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2109816</t>
+          <t>2108138</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2231678</t>
+          <t>2228273</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4422715</t>
+          <t>4424543</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4585806</t>
+          <t>4585442</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,08%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2023</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68821</t>
+          <t>68395</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>103440</t>
+          <t>102039</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90592</t>
+          <t>92714</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>136278</t>
+          <t>134633</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>168960</t>
+          <t>169204</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>224581</t>
+          <t>225073</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>532001</t>
+          <t>533402</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>566620</t>
+          <t>567046</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>589052</t>
+          <t>590697</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>634738</t>
+          <t>632616</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1136191</t>
+          <t>1135699</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1191812</t>
+          <t>1191568</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,57%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72096</t>
+          <t>71828</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>193774</t>
+          <t>192059</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>196867</t>
+          <t>196851</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>239066</t>
+          <t>240376</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>236442</t>
+          <t>243374</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>419626</t>
+          <t>419240</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>999090</t>
+          <t>1000805</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1120768</t>
+          <t>1121036</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>719585</t>
+          <t>718275</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>761784</t>
+          <t>761800</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1731890</t>
+          <t>1732276</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1915074</t>
+          <t>1908142</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,69%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62522</t>
+          <t>61178</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100517</t>
+          <t>99981</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>140460</t>
+          <t>139557</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>586643</t>
+          <t>625264</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>217056</t>
+          <t>215445</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>801012</t>
+          <t>797415</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,68%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>604163</t>
+          <t>604699</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>642158</t>
+          <t>643502</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>346723</t>
+          <t>308102</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>792906</t>
+          <t>793809</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>837034</t>
+          <t>840631</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1420990</t>
+          <t>1422601</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85163</t>
+          <t>87560</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126055</t>
+          <t>128108</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109414</t>
+          <t>107866</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>159446</t>
+          <t>159893</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>212000</t>
+          <t>210297</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>273600</t>
+          <t>272427</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>800776</t>
+          <t>798723</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>841668</t>
+          <t>839271</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>935486</t>
+          <t>935039</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>985518</t>
+          <t>987066</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1748163</t>
+          <t>1749336</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1809763</t>
+          <t>1811466</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>332435</t>
+          <t>323099</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>462865</t>
+          <t>461845</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>608615</t>
+          <t>605896</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1348448</t>
+          <t>1323806</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>995109</t>
+          <t>1002271</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1864797</t>
+          <t>1713776</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2996952</t>
+          <t>2997972</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3127382</t>
+          <t>3136718</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2363832</t>
+          <t>2388474</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3103665</t>
+          <t>3106384</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5307300</t>
+          <t>5458321</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6176988</t>
+          <t>6169826</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,03%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2C_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R2-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>192187</t>
+          <t>187932</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>240614</t>
+          <t>238129</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>237303</t>
+          <t>236345</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>286885</t>
+          <t>287566</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>441490</t>
+          <t>441286</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>511954</t>
+          <t>514275</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,2%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>453398</t>
+          <t>455883</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>501825</t>
+          <t>506080</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>401466</t>
+          <t>400785</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>451048</t>
+          <t>452006</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>870409</t>
+          <t>868088</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>940873</t>
+          <t>941077</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,08%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>268618</t>
+          <t>265309</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>324301</t>
+          <t>323060</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>307578</t>
+          <t>305076</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>367824</t>
+          <t>369552</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>589580</t>
+          <t>591832</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>673921</t>
+          <t>676860</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>637499</t>
+          <t>638740</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>693182</t>
+          <t>696491</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>600569</t>
+          <t>598841</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>660815</t>
+          <t>663317</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1256272</t>
+          <t>1253333</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1340613</t>
+          <t>1338361</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>167854</t>
+          <t>169121</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>219121</t>
+          <t>217121</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>203375</t>
+          <t>203755</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>252239</t>
+          <t>252026</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>390753</t>
+          <t>390047</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>460137</t>
+          <t>459982</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,76%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>459388</t>
+          <t>461388</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>510655</t>
+          <t>509388</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>431602</t>
+          <t>431815</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>480466</t>
+          <t>480086</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>902213</t>
+          <t>902368</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>971597</t>
+          <t>972303</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,37%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>227896</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>280920</t>
+          <t>281143</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>310265</t>
+          <t>307704</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>369336</t>
+          <t>368110</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1812,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>29,63%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>35,44%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>591588</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>553315</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>631688</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>29,87%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>35,56%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>591588</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>547132</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>631088</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>29,87%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,89%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>661302</t>
+          <t>661079</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>715020</t>
+          <t>714326</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>669276</t>
+          <t>670502</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>728347</t>
+          <t>730908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,47 +1925,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>70,37%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1389246</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1349146</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1427519</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>70,13%</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1404</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1389246</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1349746</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1433702</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>70,13%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,07%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>902370</t>
+          <t>907289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1007998</t>
+          <t>1008885</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1112673</t>
+          <t>1109829</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1224850</t>
+          <t>1221313</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2052399</t>
+          <t>2046214</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2205057</t>
+          <t>2200666</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2268545</t>
+          <t>2267658</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2374173</t>
+          <t>2369254</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2154347</t>
+          <t>2157884</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2266524</t>
+          <t>2269368</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4450684</t>
+          <t>4455075</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4603342</t>
+          <t>4609527</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>302075</t>
+          <t>304092</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>356761</t>
+          <t>357430</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>332117</t>
+          <t>337103</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>388641</t>
+          <t>393348</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>657482</t>
+          <t>654271</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>730272</t>
+          <t>732833</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,33%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>346708</t>
+          <t>346039</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>401394</t>
+          <t>399377</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>308409</t>
+          <t>303702</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>364933</t>
+          <t>359947</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>670247</t>
+          <t>667686</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>743037</t>
+          <t>746248</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,28%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>460161</t>
+          <t>461470</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>523635</t>
+          <t>527434</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>540486</t>
+          <t>539059</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>604273</t>
+          <t>608517</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1019623</t>
+          <t>1019443</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1110375</t>
+          <t>1113971</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,34%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>494312</t>
+          <t>490513</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>557786</t>
+          <t>556477</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>427911</t>
+          <t>423667</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>491698</t>
+          <t>493125</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>939756</t>
+          <t>936160</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1030508</t>
+          <t>1030688</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>307038</t>
+          <t>310547</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>365298</t>
+          <t>368769</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>384843</t>
+          <t>381095</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>443842</t>
+          <t>439482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>707368</t>
+          <t>713284</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>793900</t>
+          <t>792383</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,63%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>392325</t>
+          <t>388854</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>450585</t>
+          <t>447076</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>333332</t>
+          <t>337692</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>392331</t>
+          <t>396079</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>740897</t>
+          <t>742414</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>827429</t>
+          <t>821513</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,53%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>344320</t>
+          <t>341386</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>404429</t>
+          <t>402619</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>455821</t>
+          <t>454055</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>519125</t>
+          <t>520492</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>813937</t>
+          <t>811647</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>910770</t>
+          <t>905086</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,26%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>543310</t>
+          <t>545120</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>603419</t>
+          <t>606353</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>532776</t>
+          <t>531409</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>596080</t>
+          <t>597846</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1088870</t>
+          <t>1094554</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1185703</t>
+          <t>1187993</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,41%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1475400</t>
+          <t>1473734</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1592229</t>
+          <t>1595276</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1777181</t>
+          <t>1775443</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1901415</t>
+          <t>1895160</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3291292</t>
+          <t>3288658</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3461983</t>
+          <t>3459538</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,53%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1834550</t>
+          <t>1831503</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1951379</t>
+          <t>1953045</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1656894</t>
+          <t>1663149</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1781128</t>
+          <t>1782866</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3523105</t>
+          <t>3525550</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3693796</t>
+          <t>3696430</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,92%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>204026</t>
+          <t>205889</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>255131</t>
+          <t>253412</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>225147</t>
+          <t>223041</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>273264</t>
+          <t>272767</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>440353</t>
+          <t>442454</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>510169</t>
+          <t>514786</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,2%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>419669</t>
+          <t>421388</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>470774</t>
+          <t>468911</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>399575</t>
+          <t>400072</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>447692</t>
+          <t>449798</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>837470</t>
+          <t>832853</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>907286</t>
+          <t>905185</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,17%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>316785</t>
+          <t>318025</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>379648</t>
+          <t>380714</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>419003</t>
+          <t>419214</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>483163</t>
+          <t>484789</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>750028</t>
+          <t>752795</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>842687</t>
+          <t>842194</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,78%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>642783</t>
+          <t>641717</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>705646</t>
+          <t>704406</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>559750</t>
+          <t>558124</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>623910</t>
+          <t>623699</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1222657</t>
+          <t>1223150</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1315316</t>
+          <t>1312549</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,55%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>210004</t>
+          <t>208954</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>262767</t>
+          <t>263065</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>287229</t>
+          <t>286499</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>340617</t>
+          <t>340808</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>512830</t>
+          <t>511043</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>589078</t>
+          <t>587955</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,07%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>496785</t>
+          <t>496487</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>549548</t>
+          <t>550598</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>444394</t>
+          <t>444203</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>497782</t>
+          <t>498512</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>955485</t>
+          <t>956608</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1031733</t>
+          <t>1033520</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,91%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>225033</t>
+          <t>225727</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>280594</t>
+          <t>279644</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>327801</t>
+          <t>330259</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>392616</t>
+          <t>394486</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>568053</t>
+          <t>573145</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>652741</t>
+          <t>655539</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>656973</t>
+          <t>657923</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>712534</t>
+          <t>711840</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>651163</t>
+          <t>649293</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>715978</t>
+          <t>713520</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1328605</t>
+          <t>1325807</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1413293</t>
+          <t>1408201</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,07%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1008815</t>
+          <t>1007320</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1117687</t>
+          <t>1112032</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1316269</t>
+          <t>1312919</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1436404</t>
+          <t>1430779</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2353450</t>
+          <t>2351851</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2514349</t>
+          <t>2520436</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,32%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2276663</t>
+          <t>2282318</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2385535</t>
+          <t>2387030</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2108138</t>
+          <t>2113763</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2228273</t>
+          <t>2231623</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4424543</t>
+          <t>4418456</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4585442</t>
+          <t>4587041</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,11%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>83078</t>
+          <t>90349</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68395</t>
+          <t>72196</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>102039</t>
+          <t>111454</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>116125</t>
+          <t>126115</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92714</t>
+          <t>109741</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134633</t>
+          <t>145150</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>199203</t>
+          <t>216464</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>169204</t>
+          <t>192195</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>225073</t>
+          <t>241865</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>552363</t>
+          <t>600361</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>533402</t>
+          <t>579256</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>567046</t>
+          <t>618514</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>609205</t>
+          <t>608065</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>590697</t>
+          <t>589030</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>632616</t>
+          <t>624439</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1161569</t>
+          <t>1208425</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1135699</t>
+          <t>1183024</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1191568</t>
+          <t>1232694</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>86,51%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>144948</t>
+          <t>175476</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71828</t>
+          <t>149871</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>192059</t>
+          <t>205984</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>217129</t>
+          <t>243790</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>196851</t>
+          <t>219830</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>240376</t>
+          <t>267473</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>362077</t>
+          <t>419266</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>243374</t>
+          <t>382375</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>419240</t>
+          <t>453888</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1047916</t>
+          <t>873441</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1000805</t>
+          <t>842933</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1121036</t>
+          <t>899046</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>741522</t>
+          <t>827684</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>718275</t>
+          <t>804001</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>761800</t>
+          <t>851644</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1789439</t>
+          <t>1701125</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1732276</t>
+          <t>1666503</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1908142</t>
+          <t>1738016</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>81,97%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>79720</t>
+          <t>93059</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61178</t>
+          <t>73524</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99981</t>
+          <t>117246</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>321229</t>
+          <t>142353</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>139557</t>
+          <t>122983</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>625264</t>
+          <t>164762</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>400949</t>
+          <t>235412</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>215445</t>
+          <t>204942</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>797415</t>
+          <t>266193</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>624960</t>
+          <t>710014</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>604699</t>
+          <t>685827</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>643502</t>
+          <t>729549</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>612137</t>
+          <t>669906</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>308102</t>
+          <t>647497</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>793809</t>
+          <t>689276</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1237097</t>
+          <t>1379920</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>840631</t>
+          <t>1349139</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1422601</t>
+          <t>1410390</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>87,31%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>105188</t>
+          <t>119991</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87560</t>
+          <t>100446</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128108</t>
+          <t>141931</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>138808</t>
+          <t>161496</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>107866</t>
+          <t>142402</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>159893</t>
+          <t>183689</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>243996</t>
+          <t>281487</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>210297</t>
+          <t>253738</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>272427</t>
+          <t>311846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>821643</t>
+          <t>870071</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>798723</t>
+          <t>848131</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>839271</t>
+          <t>889616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>956124</t>
+          <t>957545</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>935039</t>
+          <t>935352</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>987066</t>
+          <t>976639</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1777767</t>
+          <t>1827617</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1749336</t>
+          <t>1797258</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1811466</t>
+          <t>1855366</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>87,97%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>412934</t>
+          <t>478875</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>323099</t>
+          <t>438065</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>461845</t>
+          <t>523629</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>793292</t>
+          <t>673754</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>605896</t>
+          <t>633462</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1323806</t>
+          <t>716404</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1206225</t>
+          <t>1152629</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1002271</t>
+          <t>1096644</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1713776</t>
+          <t>1221522</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3046883</t>
+          <t>3053887</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2997972</t>
+          <t>3009133</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3136718</t>
+          <t>3094697</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2918988</t>
+          <t>3063200</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2388474</t>
+          <t>3020550</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3106384</t>
+          <t>3103492</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5965872</t>
+          <t>6117087</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5458321</t>
+          <t>6048194</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6169826</t>
+          <t>6173072</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>84,91%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">

--- a/data/trans_orig/P2C_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R2-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son no remunerados en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son no remunerados en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son no remunerados en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son no remunerados en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son no remunerados en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
